--- a/Results/Phase 2/Methanol/methanol particulate matter results.xlsx
+++ b/Results/Phase 2/Methanol/methanol particulate matter results.xlsx
@@ -3314,85 +3314,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>7.322748685541908e-09</v>
+        <v>6.947805603319508e-09</v>
       </c>
       <c r="C33" t="n">
-        <v>6.389537346292067e-09</v>
+        <v>6.06978016851967e-09</v>
       </c>
       <c r="D33" t="n">
-        <v>9.06180240300349e-09</v>
+        <v>7.936279864429739e-09</v>
       </c>
       <c r="E33" t="n">
-        <v>8.48142713366509e-09</v>
+        <v>8.288026210291155e-09</v>
       </c>
       <c r="F33" t="n">
-        <v>8.843810914959259e-09</v>
+        <v>7.79562400750924e-09</v>
       </c>
       <c r="G33" t="n">
-        <v>1.55559534433127e-08</v>
+        <v>1.192768206893297e-08</v>
       </c>
       <c r="H33" t="n">
-        <v>8.308590223282438e-09</v>
+        <v>7.478775114476228e-09</v>
       </c>
       <c r="I33" t="n">
-        <v>9.897856924581476e-09</v>
+        <v>8.413385929751952e-09</v>
       </c>
       <c r="J33" t="n">
-        <v>1.050010601191032e-08</v>
+        <v>8.850881363252501e-09</v>
       </c>
       <c r="K33" t="n">
-        <v>1.226025795038894e-08</v>
+        <v>9.809163387265481e-09</v>
       </c>
       <c r="L33" t="n">
-        <v>1.90545834846283e-08</v>
+        <v>1.391994776397224e-08</v>
       </c>
       <c r="M33" t="n">
-        <v>9.854699142289458e-09</v>
+        <v>8.386868840675975e-09</v>
       </c>
       <c r="N33" t="n">
-        <v>1.046134613453989e-08</v>
+        <v>8.778899908615414e-09</v>
       </c>
       <c r="O33" t="n">
-        <v>1.930953208725354e-08</v>
+        <v>1.868130612449245e-08</v>
       </c>
       <c r="P33" t="n">
-        <v>7.578859400386468e-09</v>
+        <v>7.102811300410502e-09</v>
       </c>
       <c r="Q33" t="n">
-        <v>7.937571666799368e-09</v>
+        <v>7.289201859611835e-09</v>
       </c>
       <c r="R33" t="n">
-        <v>8.13783099691691e-09</v>
+        <v>7.388468841388203e-09</v>
       </c>
       <c r="S33" t="n">
-        <v>7.654645139936067e-09</v>
+        <v>7.143391149459336e-09</v>
       </c>
       <c r="T33" t="n">
-        <v>9.301759749152858e-09</v>
+        <v>8.073252840872612e-09</v>
       </c>
       <c r="U33" t="n">
-        <v>1.601291401477644e-08</v>
+        <v>1.511928398736716e-08</v>
       </c>
       <c r="V33" t="n">
-        <v>7.27293936666751e-09</v>
+        <v>6.923760217303559e-09</v>
       </c>
       <c r="W33" t="n">
-        <v>1.634311385097223e-08</v>
+        <v>1.563065098176815e-08</v>
       </c>
       <c r="X33" t="n">
-        <v>9.427053355747858e-09</v>
+        <v>8.157911974024502e-09</v>
       </c>
       <c r="Y33" t="n">
-        <v>7.610859931285898e-09</v>
+        <v>7.103854905539171e-09</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.937575449194469e-08</v>
+        <v>1.873846801714825e-08</v>
       </c>
       <c r="AA33" t="n">
-        <v>9.907505008284857e-09</v>
+        <v>8.462437815470134e-09</v>
       </c>
       <c r="AB33" t="n">
-        <v>9.060607621986128e-09</v>
+        <v>7.907461048654806e-09</v>
       </c>
     </row>
   </sheetData>
@@ -6286,85 +6286,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>5.996583732083988e-09</v>
+        <v>5.848716684336595e-09</v>
       </c>
       <c r="C33" t="n">
-        <v>5.300785015849852e-09</v>
+        <v>5.068476548761876e-09</v>
       </c>
       <c r="D33" t="n">
-        <v>6.090531778417391e-09</v>
+        <v>5.89678201743597e-09</v>
       </c>
       <c r="E33" t="n">
-        <v>7.797056690557095e-09</v>
+        <v>7.63788230674096e-09</v>
       </c>
       <c r="F33" t="n">
-        <v>6.453888880359437e-09</v>
+        <v>6.109727895268552e-09</v>
       </c>
       <c r="G33" t="n">
-        <v>6.490357290703694e-09</v>
+        <v>6.155907064638322e-09</v>
       </c>
       <c r="H33" t="n">
-        <v>6.155832896747142e-09</v>
+        <v>5.928808925026386e-09</v>
       </c>
       <c r="I33" t="n">
-        <v>6.270222837161797e-09</v>
+        <v>6.000328044890598e-09</v>
       </c>
       <c r="J33" t="n">
-        <v>6.438827254514261e-09</v>
+        <v>6.115813973459131e-09</v>
       </c>
       <c r="K33" t="n">
-        <v>6.341201230700913e-09</v>
+        <v>6.053980535974682e-09</v>
       </c>
       <c r="L33" t="n">
-        <v>6.703201437630609e-09</v>
+        <v>6.281783821195462e-09</v>
       </c>
       <c r="M33" t="n">
-        <v>6.163903499917829e-09</v>
+        <v>5.938145736093904e-09</v>
       </c>
       <c r="N33" t="n">
-        <v>6.140180513075004e-09</v>
+        <v>5.926907974336121e-09</v>
       </c>
       <c r="O33" t="n">
-        <v>1.59647641970611e-08</v>
+        <v>1.577691947707125e-08</v>
       </c>
       <c r="P33" t="n">
-        <v>6.314322892047389e-09</v>
+        <v>6.046717326309169e-09</v>
       </c>
       <c r="Q33" t="n">
-        <v>6.12796628919057e-09</v>
+        <v>5.92335221023409e-09</v>
       </c>
       <c r="R33" t="n">
-        <v>7.055657925285913e-09</v>
+        <v>6.452650442106785e-09</v>
       </c>
       <c r="S33" t="n">
-        <v>6.390509565733677e-09</v>
+        <v>6.09254731227127e-09</v>
       </c>
       <c r="T33" t="n">
-        <v>6.220352455221939e-09</v>
+        <v>5.970982171790829e-09</v>
       </c>
       <c r="U33" t="n">
-        <v>1.294866287629633e-08</v>
+        <v>1.268563695663988e-08</v>
       </c>
       <c r="V33" t="n">
-        <v>6.853666982186266e-09</v>
+        <v>6.389165175192737e-09</v>
       </c>
       <c r="W33" t="n">
-        <v>1.522544063676715e-08</v>
+        <v>1.434866601403793e-08</v>
       </c>
       <c r="X33" t="n">
-        <v>7.705307550830473e-09</v>
+        <v>6.868660419104146e-09</v>
       </c>
       <c r="Y33" t="n">
-        <v>6.860800809646662e-09</v>
+        <v>6.353757969576518e-09</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.736940717121005e-08</v>
+        <v>1.71353545033523e-08</v>
       </c>
       <c r="AA33" t="n">
-        <v>6.830660411087586e-09</v>
+        <v>6.337264738506122e-09</v>
       </c>
       <c r="AB33" t="n">
-        <v>6.020316777265262e-09</v>
+        <v>5.850516668877453e-09</v>
       </c>
     </row>
   </sheetData>
@@ -9258,85 +9258,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>6.852838875210632e-09</v>
+        <v>6.563337990549071e-09</v>
       </c>
       <c r="C33" t="n">
-        <v>6.161351456758866e-09</v>
+        <v>5.820076283635961e-09</v>
       </c>
       <c r="D33" t="n">
-        <v>7.279868702875308e-09</v>
+        <v>6.793652281349973e-09</v>
       </c>
       <c r="E33" t="n">
-        <v>8.24194084300648e-09</v>
+        <v>8.064515745763859e-09</v>
       </c>
       <c r="F33" t="n">
-        <v>7.611409368726115e-09</v>
+        <v>6.984159170372305e-09</v>
       </c>
       <c r="G33" t="n">
-        <v>1.316657551662977e-08</v>
+        <v>1.039681083625198e-08</v>
       </c>
       <c r="H33" t="n">
-        <v>7.033219301111808e-09</v>
+        <v>6.641318335777176e-09</v>
       </c>
       <c r="I33" t="n">
-        <v>8.12395086877307e-09</v>
+        <v>7.279576211752821e-09</v>
       </c>
       <c r="J33" t="n">
-        <v>9.555696196685345e-09</v>
+        <v>8.188568274903563e-09</v>
       </c>
       <c r="K33" t="n">
-        <v>1.081051609575056e-08</v>
+        <v>8.92656725768485e-09</v>
       </c>
       <c r="L33" t="n">
-        <v>1.641260924026823e-08</v>
+        <v>1.224511207368615e-08</v>
       </c>
       <c r="M33" t="n">
-        <v>8.407775976177436e-09</v>
+        <v>7.444931165476607e-09</v>
       </c>
       <c r="N33" t="n">
-        <v>8.144709009556854e-09</v>
+        <v>7.310736606810854e-09</v>
       </c>
       <c r="O33" t="n">
-        <v>1.787695556578556e-08</v>
+        <v>1.746350791414622e-08</v>
       </c>
       <c r="P33" t="n">
-        <v>7.551672412882528e-09</v>
+        <v>6.988043071783656e-09</v>
       </c>
       <c r="Q33" t="n">
-        <v>7.123993936393793e-09</v>
+        <v>6.708263866403096e-09</v>
       </c>
       <c r="R33" t="n">
-        <v>7.084947100170656e-09</v>
+        <v>6.674810220967421e-09</v>
       </c>
       <c r="S33" t="n">
-        <v>7.242488680225749e-09</v>
+        <v>6.796403525575585e-09</v>
       </c>
       <c r="T33" t="n">
-        <v>7.512631721607431e-09</v>
+        <v>6.929044545974983e-09</v>
       </c>
       <c r="U33" t="n">
-        <v>1.475701897450729e-08</v>
+        <v>1.414399102264212e-08</v>
       </c>
       <c r="V33" t="n">
-        <v>6.753679997570376e-09</v>
+        <v>6.510410744668461e-09</v>
       </c>
       <c r="W33" t="n">
-        <v>1.657660328633619e-08</v>
+        <v>1.554183252389105e-08</v>
       </c>
       <c r="X33" t="n">
-        <v>9.494694387587134e-09</v>
+        <v>8.09649343787445e-09</v>
       </c>
       <c r="Y33" t="n">
-        <v>7.300146491032236e-09</v>
+        <v>6.818864755901684e-09</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.863357533549537e-08</v>
+        <v>1.812370788361978e-08</v>
       </c>
       <c r="AA33" t="n">
-        <v>7.938466174204235e-09</v>
+        <v>7.196916596169637e-09</v>
       </c>
       <c r="AB33" t="n">
-        <v>8.670328793520107e-09</v>
+        <v>7.576003185458591e-09</v>
       </c>
     </row>
   </sheetData>
@@ -12230,85 +12230,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>6.512338490545605e-09</v>
+        <v>6.310863378414858e-09</v>
       </c>
       <c r="C33" t="n">
-        <v>5.869554996865015e-09</v>
+        <v>5.600714107710172e-09</v>
       </c>
       <c r="D33" t="n">
-        <v>7.427898936402152e-09</v>
+        <v>6.834971037802822e-09</v>
       </c>
       <c r="E33" t="n">
-        <v>8.342291822494386e-09</v>
+        <v>8.090904362422715e-09</v>
       </c>
       <c r="F33" t="n">
-        <v>7.234365555302887e-09</v>
+        <v>6.721100649931674e-09</v>
       </c>
       <c r="G33" t="n">
-        <v>1.202231916173503e-08</v>
+        <v>9.678914196240602e-09</v>
       </c>
       <c r="H33" t="n">
-        <v>6.534172974984931e-09</v>
+        <v>6.307121511718125e-09</v>
       </c>
       <c r="I33" t="n">
-        <v>7.440007511053617e-09</v>
+        <v>6.836952373445116e-09</v>
       </c>
       <c r="J33" t="n">
-        <v>8.933671369449256e-09</v>
+        <v>7.775463768499734e-09</v>
       </c>
       <c r="K33" t="n">
-        <v>7.295597669878764e-09</v>
+        <v>6.780936319518961e-09</v>
       </c>
       <c r="L33" t="n">
-        <v>1.447728564421566e-08</v>
+        <v>1.105720397980643e-08</v>
       </c>
       <c r="M33" t="n">
-        <v>7.981872658995663e-09</v>
+        <v>7.150008216069567e-09</v>
       </c>
       <c r="N33" t="n">
-        <v>6.966192593947851e-09</v>
+        <v>6.569926033620423e-09</v>
       </c>
       <c r="O33" t="n">
-        <v>1.70567545858553e-08</v>
+        <v>1.678601301506581e-08</v>
       </c>
       <c r="P33" t="n">
-        <v>7.132875140288912e-09</v>
+        <v>6.691251831835311e-09</v>
       </c>
       <c r="Q33" t="n">
-        <v>6.958844413297123e-09</v>
+        <v>6.568027290089485e-09</v>
       </c>
       <c r="R33" t="n">
-        <v>6.493210982565253e-09</v>
+        <v>6.286102772468363e-09</v>
       </c>
       <c r="S33" t="n">
-        <v>6.937566183157949e-09</v>
+        <v>6.56854287661062e-09</v>
       </c>
       <c r="T33" t="n">
-        <v>6.885104966658937e-09</v>
+        <v>6.516359139362752e-09</v>
       </c>
       <c r="U33" t="n">
-        <v>1.420229921706787e-08</v>
+        <v>1.371011674032377e-08</v>
       </c>
       <c r="V33" t="n">
-        <v>6.616907425344058e-09</v>
+        <v>6.384258460442361e-09</v>
       </c>
       <c r="W33" t="n">
-        <v>1.596814701661604e-08</v>
+        <v>1.506441550437225e-08</v>
       </c>
       <c r="X33" t="n">
-        <v>1.086523128852118e-08</v>
+        <v>8.858956170230509e-09</v>
       </c>
       <c r="Y33" t="n">
-        <v>8.106964306983932e-09</v>
+        <v>7.253402293357868e-09</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.840315891510542e-08</v>
+        <v>1.793344206257147e-08</v>
       </c>
       <c r="AA33" t="n">
-        <v>7.242747164341343e-09</v>
+        <v>6.737674781849342e-09</v>
       </c>
       <c r="AB33" t="n">
-        <v>8.435063998724327e-09</v>
+        <v>7.391585688021921e-09</v>
       </c>
     </row>
   </sheetData>
@@ -15202,85 +15202,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>6.364974356976151e-09</v>
+        <v>6.184553684521984e-09</v>
       </c>
       <c r="C33" t="n">
-        <v>5.569287411148227e-09</v>
+        <v>5.349527747057969e-09</v>
       </c>
       <c r="D33" t="n">
-        <v>6.696698503329378e-09</v>
+        <v>6.371596691273931e-09</v>
       </c>
       <c r="E33" t="n">
-        <v>8.11195413239388e-09</v>
+        <v>7.926265737765174e-09</v>
       </c>
       <c r="F33" t="n">
-        <v>7.144125108098867e-09</v>
+        <v>6.630713073307881e-09</v>
       </c>
       <c r="G33" t="n">
-        <v>1.102734001162638e-08</v>
+        <v>9.071286906101939e-09</v>
       </c>
       <c r="H33" t="n">
-        <v>6.452264550587115e-09</v>
+        <v>6.219258810726343e-09</v>
       </c>
       <c r="I33" t="n">
-        <v>7.055200524882373e-09</v>
+        <v>6.57664907555868e-09</v>
       </c>
       <c r="J33" t="n">
-        <v>8.314936417531358e-09</v>
+        <v>7.376591785617401e-09</v>
       </c>
       <c r="K33" t="n">
-        <v>7.259770719978979e-09</v>
+        <v>6.722484041192159e-09</v>
       </c>
       <c r="L33" t="n">
-        <v>1.250517542351503e-08</v>
+        <v>9.899880991391489e-09</v>
       </c>
       <c r="M33" t="n">
-        <v>7.547923107590368e-09</v>
+        <v>6.870363230443509e-09</v>
       </c>
       <c r="N33" t="n">
-        <v>6.355025335960406e-09</v>
+        <v>6.170704636950088e-09</v>
       </c>
       <c r="O33" t="n">
-        <v>1.687681410135302e-08</v>
+        <v>1.659738762181011e-08</v>
       </c>
       <c r="P33" t="n">
-        <v>6.746776854346943e-09</v>
+        <v>6.421772620952596e-09</v>
       </c>
       <c r="Q33" t="n">
-        <v>6.780655939634925e-09</v>
+        <v>6.427016141500223e-09</v>
       </c>
       <c r="R33" t="n">
-        <v>6.636454986244708e-09</v>
+        <v>6.328105930475142e-09</v>
       </c>
       <c r="S33" t="n">
-        <v>6.854519169142668e-09</v>
+        <v>6.482771955163477e-09</v>
       </c>
       <c r="T33" t="n">
-        <v>6.904094904062545e-09</v>
+        <v>6.487266654915639e-09</v>
       </c>
       <c r="U33" t="n">
-        <v>1.391587789808897e-08</v>
+        <v>1.338519751430439e-08</v>
       </c>
       <c r="V33" t="n">
-        <v>6.593533879361308e-09</v>
+        <v>6.334927732722669e-09</v>
       </c>
       <c r="W33" t="n">
-        <v>1.483373981047973e-08</v>
+        <v>1.423149389446892e-08</v>
       </c>
       <c r="X33" t="n">
-        <v>1.109551105225423e-08</v>
+        <v>8.990345709416216e-09</v>
       </c>
       <c r="Y33" t="n">
-        <v>8.855186191632822e-09</v>
+        <v>7.648452684372282e-09</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.812797640807074e-08</v>
+        <v>1.772891522377575e-08</v>
       </c>
       <c r="AA33" t="n">
-        <v>7.169677084279721e-09</v>
+        <v>6.654326269690721e-09</v>
       </c>
       <c r="AB33" t="n">
-        <v>8.037199212933561e-09</v>
+        <v>7.129571449596504e-09</v>
       </c>
     </row>
   </sheetData>
@@ -18174,85 +18174,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>6.229336410987177e-09</v>
+        <v>6.024500069693944e-09</v>
       </c>
       <c r="C33" t="n">
-        <v>5.244560151072381e-09</v>
+        <v>5.098958385288339e-09</v>
       </c>
       <c r="D33" t="n">
-        <v>7.429176607817664e-09</v>
+        <v>6.715187929315261e-09</v>
       </c>
       <c r="E33" t="n">
-        <v>8.218851468222346e-09</v>
+        <v>7.91938278826004e-09</v>
       </c>
       <c r="F33" t="n">
-        <v>6.426581954533317e-09</v>
+        <v>6.126886109345784e-09</v>
       </c>
       <c r="G33" t="n">
-        <v>7.674696822199437e-09</v>
+        <v>6.936024989499652e-09</v>
       </c>
       <c r="H33" t="n">
-        <v>6.658714448338318e-09</v>
+        <v>6.253425297914646e-09</v>
       </c>
       <c r="I33" t="n">
-        <v>6.910567265766287e-09</v>
+        <v>6.40754183012064e-09</v>
       </c>
       <c r="J33" t="n">
-        <v>7.058041220249598e-09</v>
+        <v>6.53415074656823e-09</v>
       </c>
       <c r="K33" t="n">
-        <v>8.205030724892197e-09</v>
+        <v>7.217600797383674e-09</v>
       </c>
       <c r="L33" t="n">
-        <v>8.739544977500689e-09</v>
+        <v>7.589467519361445e-09</v>
       </c>
       <c r="M33" t="n">
-        <v>6.777789082555471e-09</v>
+        <v>6.343885261994696e-09</v>
       </c>
       <c r="N33" t="n">
-        <v>7.555338148596619e-09</v>
+        <v>6.807893365885959e-09</v>
       </c>
       <c r="O33" t="n">
-        <v>1.640264297766156e-08</v>
+        <v>1.617186354528933e-08</v>
       </c>
       <c r="P33" t="n">
-        <v>6.950388424235927e-09</v>
+        <v>6.464904805538833e-09</v>
       </c>
       <c r="Q33" t="n">
-        <v>6.798770701343261e-09</v>
+        <v>6.358568696917331e-09</v>
       </c>
       <c r="R33" t="n">
-        <v>6.783346680520197e-09</v>
+        <v>6.328287148181369e-09</v>
       </c>
       <c r="S33" t="n">
-        <v>6.603464183222578e-09</v>
+        <v>6.267219115954712e-09</v>
       </c>
       <c r="T33" t="n">
-        <v>6.512935911663117e-09</v>
+        <v>6.181636223915813e-09</v>
       </c>
       <c r="U33" t="n">
-        <v>1.332284914859669e-08</v>
+        <v>1.301309091074082e-08</v>
       </c>
       <c r="V33" t="n">
-        <v>6.20365383767067e-09</v>
+        <v>6.016429836651745e-09</v>
       </c>
       <c r="W33" t="n">
-        <v>1.433541936435178e-08</v>
+        <v>1.390471708633715e-08</v>
       </c>
       <c r="X33" t="n">
-        <v>6.902398505851358e-09</v>
+        <v>6.410030003501307e-09</v>
       </c>
       <c r="Y33" t="n">
-        <v>6.280208727917089e-09</v>
+        <v>6.046935889274127e-09</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.783652447121808e-08</v>
+        <v>1.747438510417517e-08</v>
       </c>
       <c r="AA33" t="n">
-        <v>6.823612549853241e-09</v>
+        <v>6.36980057159188e-09</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.372538839695209e-08</v>
+        <v>1.036570035718267e-08</v>
       </c>
     </row>
   </sheetData>
@@ -21146,85 +21146,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>6.248757749117084e-09</v>
+        <v>6.002228567565331e-09</v>
       </c>
       <c r="C33" t="n">
-        <v>5.466620206558161e-09</v>
+        <v>5.201016610768285e-09</v>
       </c>
       <c r="D33" t="n">
-        <v>6.354242901807093e-09</v>
+        <v>6.054890667652131e-09</v>
       </c>
       <c r="E33" t="n">
-        <v>8.101677018876146e-09</v>
+        <v>7.818306033211486e-09</v>
       </c>
       <c r="F33" t="n">
-        <v>6.703667214467653e-09</v>
+        <v>6.258979014524635e-09</v>
       </c>
       <c r="G33" t="n">
-        <v>6.518086721723127e-09</v>
+        <v>6.179331130267841e-09</v>
       </c>
       <c r="H33" t="n">
-        <v>6.366581024726178e-09</v>
+        <v>6.049835794401757e-09</v>
       </c>
       <c r="I33" t="n">
-        <v>6.499662138773341e-09</v>
+        <v>6.135514037797413e-09</v>
       </c>
       <c r="J33" t="n">
-        <v>6.496260578889638e-09</v>
+        <v>6.155721738271948e-09</v>
       </c>
       <c r="K33" t="n">
-        <v>6.277242441512722e-09</v>
+        <v>6.013139408002666e-09</v>
       </c>
       <c r="L33" t="n">
-        <v>6.460472259179226e-09</v>
+        <v>6.145332533836714e-09</v>
       </c>
       <c r="M33" t="n">
-        <v>6.114854109570257e-09</v>
+        <v>5.911551525272769e-09</v>
       </c>
       <c r="N33" t="n">
-        <v>6.747349370152608e-09</v>
+        <v>6.295085379193198e-09</v>
       </c>
       <c r="O33" t="n">
-        <v>1.701153836396945e-08</v>
+        <v>1.650847903625416e-08</v>
       </c>
       <c r="P33" t="n">
-        <v>6.305146072781583e-09</v>
+        <v>6.038241836878031e-09</v>
       </c>
       <c r="Q33" t="n">
-        <v>6.132010339264769e-09</v>
+        <v>5.929126580399258e-09</v>
       </c>
       <c r="R33" t="n">
-        <v>7.138525076445498e-09</v>
+        <v>6.504690289335293e-09</v>
       </c>
       <c r="S33" t="n">
-        <v>6.388657492772101e-09</v>
+        <v>6.098375264674445e-09</v>
       </c>
       <c r="T33" t="n">
-        <v>6.129874524714591e-09</v>
+        <v>5.919765887109607e-09</v>
       </c>
       <c r="U33" t="n">
-        <v>1.273954292523891e-08</v>
+        <v>1.259381211176327e-08</v>
       </c>
       <c r="V33" t="n">
-        <v>6.311624366889208e-09</v>
+        <v>6.053139172384285e-09</v>
       </c>
       <c r="W33" t="n">
-        <v>1.456450877111035e-08</v>
+        <v>1.39870261587453e-08</v>
       </c>
       <c r="X33" t="n">
-        <v>6.985910151310879e-09</v>
+        <v>6.438469677978931e-09</v>
       </c>
       <c r="Y33" t="n">
-        <v>6.274293877919951e-09</v>
+        <v>6.007642027324759e-09</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.798917869318678e-08</v>
+        <v>1.754971442338923e-08</v>
       </c>
       <c r="AA33" t="n">
-        <v>6.428023524512417e-09</v>
+        <v>6.099503273025173e-09</v>
       </c>
       <c r="AB33" t="n">
-        <v>5.950598679847424e-09</v>
+        <v>5.810454318662494e-09</v>
       </c>
     </row>
   </sheetData>
@@ -24118,85 +24118,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>6.529417318454877e-09</v>
+        <v>6.17519425854934e-09</v>
       </c>
       <c r="C33" t="n">
-        <v>5.43445643885569e-09</v>
+        <v>5.146592050553801e-09</v>
       </c>
       <c r="D33" t="n">
-        <v>6.396287938019998e-09</v>
+        <v>6.077752592827684e-09</v>
       </c>
       <c r="E33" t="n">
-        <v>8.46107639137895e-09</v>
+        <v>8.050966452164684e-09</v>
       </c>
       <c r="F33" t="n">
-        <v>6.529953403365686e-09</v>
+        <v>6.151549356922056e-09</v>
       </c>
       <c r="G33" t="n">
-        <v>6.267315719325882e-09</v>
+        <v>6.01596404033123e-09</v>
       </c>
       <c r="H33" t="n">
-        <v>6.189106669135099e-09</v>
+        <v>5.947374114666148e-09</v>
       </c>
       <c r="I33" t="n">
-        <v>6.228249023922633e-09</v>
+        <v>5.974438707438005e-09</v>
       </c>
       <c r="J33" t="n">
-        <v>6.423934363691559e-09</v>
+        <v>6.106809189579326e-09</v>
       </c>
       <c r="K33" t="n">
-        <v>6.133345779694027e-09</v>
+        <v>5.923055560391007e-09</v>
       </c>
       <c r="L33" t="n">
-        <v>6.487478951429006e-09</v>
+        <v>6.154690306248522e-09</v>
       </c>
       <c r="M33" t="n">
-        <v>6.080349723193322e-09</v>
+        <v>5.888105070793209e-09</v>
       </c>
       <c r="N33" t="n">
-        <v>6.283792235126432e-09</v>
+        <v>6.013608903296669e-09</v>
       </c>
       <c r="O33" t="n">
-        <v>1.707367929519748e-08</v>
+        <v>1.654361880480472e-08</v>
       </c>
       <c r="P33" t="n">
-        <v>6.464669476133723e-09</v>
+        <v>6.139355200129725e-09</v>
       </c>
       <c r="Q33" t="n">
-        <v>6.076481350803085e-09</v>
+        <v>5.891626194700399e-09</v>
       </c>
       <c r="R33" t="n">
-        <v>7.32932269362599e-09</v>
+        <v>6.611781102806394e-09</v>
       </c>
       <c r="S33" t="n">
-        <v>6.366998258360401e-09</v>
+        <v>6.077653409319507e-09</v>
       </c>
       <c r="T33" t="n">
-        <v>6.071308410396822e-09</v>
+        <v>5.883502465853505e-09</v>
       </c>
       <c r="U33" t="n">
-        <v>1.26667877014105e-08</v>
+        <v>1.24831350398286e-08</v>
       </c>
       <c r="V33" t="n">
-        <v>6.969043023165601e-09</v>
+        <v>6.458843300557281e-09</v>
       </c>
       <c r="W33" t="n">
-        <v>1.471809578893422e-08</v>
+        <v>1.402331337414503e-08</v>
       </c>
       <c r="X33" t="n">
-        <v>7.179344637959448e-09</v>
+        <v>6.559314464417381e-09</v>
       </c>
       <c r="Y33" t="n">
-        <v>6.311764506219301e-09</v>
+        <v>6.028416913120231e-09</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.770462859284787e-08</v>
+        <v>1.736547516346199e-08</v>
       </c>
       <c r="AA33" t="n">
-        <v>6.428787843480373e-09</v>
+        <v>6.099095703314342e-09</v>
       </c>
       <c r="AB33" t="n">
-        <v>6.079649933442484e-09</v>
+        <v>5.88448257758902e-09</v>
       </c>
     </row>
   </sheetData>
@@ -27090,85 +27090,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>6.7367092660522e-09</v>
+        <v>6.463616826857702e-09</v>
       </c>
       <c r="C33" t="n">
-        <v>5.79297330397258e-09</v>
+        <v>5.564346565802071e-09</v>
       </c>
       <c r="D33" t="n">
-        <v>7.601057840860092e-09</v>
+        <v>6.949275239395769e-09</v>
       </c>
       <c r="E33" t="n">
-        <v>8.199624751302802e-09</v>
+        <v>8.017451108835141e-09</v>
       </c>
       <c r="F33" t="n">
-        <v>7.25303190281405e-09</v>
+        <v>6.746907768633876e-09</v>
       </c>
       <c r="G33" t="n">
-        <v>1.264600142371347e-08</v>
+        <v>1.011562238784344e-08</v>
       </c>
       <c r="H33" t="n">
-        <v>6.994948726294737e-09</v>
+        <v>6.587598274635067e-09</v>
       </c>
       <c r="I33" t="n">
-        <v>8.353691389379539e-09</v>
+        <v>7.386386480550771e-09</v>
       </c>
       <c r="J33" t="n">
-        <v>9.23191503385334e-09</v>
+        <v>7.989418178664046e-09</v>
       </c>
       <c r="K33" t="n">
-        <v>9.603336160631435e-09</v>
+        <v>8.199080731009475e-09</v>
       </c>
       <c r="L33" t="n">
-        <v>1.496741615137951e-08</v>
+        <v>1.142778634860021e-08</v>
       </c>
       <c r="M33" t="n">
-        <v>8.311500147087805e-09</v>
+        <v>7.391787101648399e-09</v>
       </c>
       <c r="N33" t="n">
-        <v>9.135181314941178e-09</v>
+        <v>7.864133499968989e-09</v>
       </c>
       <c r="O33" t="n">
-        <v>1.762226186918684e-08</v>
+        <v>1.722370866130307e-08</v>
       </c>
       <c r="P33" t="n">
-        <v>7.559407097847862e-09</v>
+        <v>6.963722674238336e-09</v>
       </c>
       <c r="Q33" t="n">
-        <v>7.08673003812069e-09</v>
+        <v>6.659631412572166e-09</v>
       </c>
       <c r="R33" t="n">
-        <v>7.31473266388835e-09</v>
+        <v>6.775466064980499e-09</v>
       </c>
       <c r="S33" t="n">
-        <v>7.061848436166314e-09</v>
+        <v>6.667042668705475e-09</v>
       </c>
       <c r="T33" t="n">
-        <v>7.702376133996108e-09</v>
+        <v>7.008577853472399e-09</v>
       </c>
       <c r="U33" t="n">
-        <v>1.428603358553178e-08</v>
+        <v>1.375087864267898e-08</v>
       </c>
       <c r="V33" t="n">
-        <v>6.635583307540519e-09</v>
+        <v>6.408954978027833e-09</v>
       </c>
       <c r="W33" t="n">
-        <v>1.483110137250389e-08</v>
+        <v>1.437154510725972e-08</v>
       </c>
       <c r="X33" t="n">
-        <v>9.728884244279306e-09</v>
+        <v>8.203608853798457e-09</v>
       </c>
       <c r="Y33" t="n">
-        <v>7.153586090080187e-09</v>
+        <v>6.701748350676015e-09</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.845813311686653e-08</v>
+        <v>1.797448707796932e-08</v>
       </c>
       <c r="AA33" t="n">
-        <v>7.690807118194338e-09</v>
+        <v>7.019818677314866e-09</v>
       </c>
       <c r="AB33" t="n">
-        <v>8.275299398842603e-09</v>
+        <v>7.319756637268212e-09</v>
       </c>
     </row>
   </sheetData>
@@ -30062,85 +30062,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>6.320165707836757e-09</v>
+        <v>6.155698346249785e-09</v>
       </c>
       <c r="C33" t="n">
-        <v>5.715683723953218e-09</v>
+        <v>5.46122718937738e-09</v>
       </c>
       <c r="D33" t="n">
-        <v>6.556126164727381e-09</v>
+        <v>6.286166716911197e-09</v>
       </c>
       <c r="E33" t="n">
-        <v>8.244590764501245e-09</v>
+        <v>8.004208831363652e-09</v>
       </c>
       <c r="F33" t="n">
-        <v>6.732722652067684e-09</v>
+        <v>6.389517713102145e-09</v>
       </c>
       <c r="G33" t="n">
-        <v>1.087483826290983e-08</v>
+        <v>9.013859821047449e-09</v>
       </c>
       <c r="H33" t="n">
-        <v>6.434387342215321e-09</v>
+        <v>6.208258503844086e-09</v>
       </c>
       <c r="I33" t="n">
-        <v>6.686708103183377e-09</v>
+        <v>6.359230121908523e-09</v>
       </c>
       <c r="J33" t="n">
-        <v>8.323443435122155e-09</v>
+        <v>7.385332278500485e-09</v>
       </c>
       <c r="K33" t="n">
-        <v>6.933340958890002e-09</v>
+        <v>6.524293516487997e-09</v>
       </c>
       <c r="L33" t="n">
-        <v>9.374583836748509e-09</v>
+        <v>8.04054569649661e-09</v>
       </c>
       <c r="M33" t="n">
-        <v>6.62553322871942e-09</v>
+        <v>6.328597432245092e-09</v>
       </c>
       <c r="N33" t="n">
-        <v>6.581438409373487e-09</v>
+        <v>6.303328195310062e-09</v>
       </c>
       <c r="O33" t="n">
-        <v>1.657210923288926e-08</v>
+        <v>1.637000566867982e-08</v>
       </c>
       <c r="P33" t="n">
-        <v>7.411956149295631e-09</v>
+        <v>6.827706555292793e-09</v>
       </c>
       <c r="Q33" t="n">
-        <v>6.718843468111893e-09</v>
+        <v>6.394879698936964e-09</v>
       </c>
       <c r="R33" t="n">
-        <v>7.274683334144039e-09</v>
+        <v>6.696146269528552e-09</v>
       </c>
       <c r="S33" t="n">
-        <v>6.834904829962422e-09</v>
+        <v>6.476704450495628e-09</v>
       </c>
       <c r="T33" t="n">
-        <v>6.583485373576349e-09</v>
+        <v>6.300868274292289e-09</v>
       </c>
       <c r="U33" t="n">
-        <v>1.32891056761194e-08</v>
+        <v>1.30587646212369e-08</v>
       </c>
       <c r="V33" t="n">
-        <v>6.545845408922861e-09</v>
+        <v>6.30355165746973e-09</v>
       </c>
       <c r="W33" t="n">
-        <v>1.483172236205664e-08</v>
+        <v>1.42735547078174e-08</v>
       </c>
       <c r="X33" t="n">
-        <v>8.354973324705364e-09</v>
+        <v>7.357955671958779e-09</v>
       </c>
       <c r="Y33" t="n">
-        <v>7.690648938399663e-09</v>
+        <v>6.967192266024834e-09</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.753272014405403e-08</v>
+        <v>1.729579359700692e-08</v>
       </c>
       <c r="AA33" t="n">
-        <v>6.653084959884306e-09</v>
+        <v>6.348290913161095e-09</v>
       </c>
       <c r="AB33" t="n">
-        <v>5.346589703308045e-08</v>
+        <v>3.340420907183468e-08</v>
       </c>
     </row>
   </sheetData>
